--- a/data/trans_orig/P68-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P68-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31941</t>
+          <t>32798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54640</t>
+          <t>55206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20146</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>39668</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87304</t>
+          <t>87415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109860</t>
+          <t>109294</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132559</t>
+          <t>131702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72647</t>
+          <t>71302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90824</t>
+          <t>90310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188166</t>
+          <t>188055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219133</t>
+          <t>218185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56491</t>
+          <t>57228</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90202</t>
+          <t>88277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43408</t>
+          <t>42903</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87192</t>
+          <t>87353</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125912</t>
+          <t>124534</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180279</t>
+          <t>182204</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213990</t>
+          <t>213253</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88604</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108172</t>
+          <t>108477</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276581</t>
+          <t>277959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315301</t>
+          <t>315140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26330</t>
+          <t>25949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47660</t>
+          <t>47044</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>14026</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30537</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45620</t>
+          <t>45207</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74708</t>
+          <t>73437</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126989</t>
+          <t>127605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148319</t>
+          <t>148700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63148</t>
+          <t>63371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78677</t>
+          <t>79659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>194898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>222715</t>
+          <t>223128</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45072</t>
+          <t>45671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71575</t>
+          <t>71928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32546</t>
+          <t>32491</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66440</t>
+          <t>65913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96642</t>
+          <t>97637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151969</t>
+          <t>151616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178472</t>
+          <t>177873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102081</t>
+          <t>102136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119060</t>
+          <t>119095</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>261529</t>
+          <t>260534</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291731</t>
+          <t>292258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41422</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78159</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>95118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36470</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45767</t>
+          <t>45863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117882</t>
+          <t>118448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138363</t>
+          <t>138614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31258</t>
+          <t>31335</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>54037</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>44371</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68872</t>
+          <t>70832</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101924</t>
+          <t>100891</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>123593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60965</t>
+          <t>61787</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74808</t>
+          <t>74819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168874</t>
+          <t>166914</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193030</t>
+          <t>193375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73942</t>
+          <t>73395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105450</t>
+          <t>106574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>54986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112692</t>
+          <t>113759</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153089</t>
+          <t>152953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230399</t>
+          <t>229275</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>261907</t>
+          <t>262454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>124021</t>
+          <t>124584</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146669</t>
+          <t>148082</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>362331</t>
+          <t>362467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>402728</t>
+          <t>401661</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92786</t>
+          <t>90427</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128891</t>
+          <t>126190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38214</t>
+          <t>37611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64003</t>
+          <t>64645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137497</t>
+          <t>137232</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181428</t>
+          <t>180067</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>330089</t>
+          <t>332790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>366194</t>
+          <t>368553</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>174977</t>
+          <t>174335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>200766</t>
+          <t>201369</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>516532</t>
+          <t>517893</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>560463</t>
+          <t>560728</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>432161</t>
+          <t>434510</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>506905</t>
+          <t>510003</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>195809</t>
+          <t>196389</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>249326</t>
+          <t>247541</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>644460</t>
+          <t>646055</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>737682</t>
+          <t>740870</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1386530</t>
+          <t>1383432</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1461274</t>
+          <t>1458925</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>772138</t>
+          <t>773923</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>825655</t>
+          <t>825075</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2177217</t>
+          <t>2174029</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2270439</t>
+          <t>2268844</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30130</t>
+          <t>29566</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52508</t>
+          <t>51062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38630</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56999</t>
+          <t>57010</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85793</t>
+          <t>86051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73308</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95686</t>
+          <t>96250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48840</t>
+          <t>47796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66570</t>
+          <t>66269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127493</t>
+          <t>127235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156287</t>
+          <t>156276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43954</t>
+          <t>45092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69149</t>
+          <t>68872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>24750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46175</t>
+          <t>45858</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72894</t>
+          <t>74619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107878</t>
+          <t>109015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103091</t>
+          <t>103368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128286</t>
+          <t>127148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76513</t>
+          <t>76830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97590</t>
+          <t>97938</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>187050</t>
+          <t>185913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>222034</t>
+          <t>220309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>16766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>34600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28074</t>
+          <t>26936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32815</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>57441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108521</t>
+          <t>108601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126443</t>
+          <t>126435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54292</t>
+          <t>55430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70630</t>
+          <t>70968</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168878</t>
+          <t>168126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192752</t>
+          <t>192948</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36948</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60273</t>
+          <t>59230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20340</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39788</t>
+          <t>39215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60302</t>
+          <t>62236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91385</t>
+          <t>93020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82416</t>
+          <t>83459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105741</t>
+          <t>106808</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62660</t>
+          <t>63233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82108</t>
+          <t>82448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153752</t>
+          <t>152117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184835</t>
+          <t>182901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>19922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>39933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>58084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72672</t>
+          <t>72521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36778</t>
+          <t>37427</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99976</t>
+          <t>99092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119865</t>
+          <t>119103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>33857</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56060</t>
+          <t>55586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22382</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47247</t>
+          <t>47305</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72663</t>
+          <t>72309</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61230</t>
+          <t>61704</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83394</t>
+          <t>83433</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32910</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46137</t>
+          <t>46039</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99919</t>
+          <t>100273</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125335</t>
+          <t>125277</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,59%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42742</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70201</t>
+          <t>69173</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59262</t>
+          <t>58738</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>82341</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119744</t>
+          <t>119882</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>202723</t>
+          <t>203751</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>230182</t>
+          <t>231713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>122903</t>
+          <t>123427</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147995</t>
+          <t>146906</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>335345</t>
+          <t>335207</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>371614</t>
+          <t>372748</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61080</t>
+          <t>60630</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20483</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43470</t>
+          <t>43631</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61059</t>
+          <t>63251</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96625</t>
+          <t>96853</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>301152</t>
+          <t>301602</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>327321</t>
+          <t>327261</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>216105</t>
+          <t>215944</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239092</t>
+          <t>239230</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>525182</t>
+          <t>524954</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>560748</t>
+          <t>558556</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>300778</t>
+          <t>300958</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>363978</t>
+          <t>365159</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190384</t>
+          <t>190759</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>244971</t>
+          <t>242807</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>506992</t>
+          <t>506861</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>587553</t>
+          <t>591211</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1054727</t>
+          <t>1053546</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1117927</t>
+          <t>1117747</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>703745</t>
+          <t>705909</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>758332</t>
+          <t>757957</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1779868</t>
+          <t>1776210</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1860429</t>
+          <t>1860560</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47068</t>
+          <t>47092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70552</t>
+          <t>71889</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50813</t>
+          <t>51027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84173</t>
+          <t>85226</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115694</t>
+          <t>115371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65614</t>
+          <t>64277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89098</t>
+          <t>89074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50162</t>
+          <t>49948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70368</t>
+          <t>69419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121447</t>
+          <t>121770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152968</t>
+          <t>151915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71604</t>
+          <t>69432</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97974</t>
+          <t>96238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52905</t>
+          <t>53593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107435</t>
+          <t>107553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141981</t>
+          <t>143725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72323</t>
+          <t>74059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98693</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60775</t>
+          <t>60087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82126</t>
+          <t>81049</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141996</t>
+          <t>140252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176542</t>
+          <t>176424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,13%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>14248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29734</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7063</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>20413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45077</t>
+          <t>45893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93142</t>
+          <t>92797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109190</t>
+          <t>108628</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63027</t>
+          <t>62923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76273</t>
+          <t>76052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161135</t>
+          <t>160319</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>181632</t>
+          <t>181421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23081</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21976</t>
+          <t>21368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39290</t>
+          <t>40015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49661</t>
+          <t>49543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75600</t>
+          <t>76432</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69754</t>
+          <t>69861</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89099</t>
+          <t>88730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40687</t>
+          <t>39962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58001</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116557</t>
+          <t>115725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142496</t>
+          <t>142614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23793</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31590</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56180</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71077</t>
+          <t>71548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43720</t>
+          <t>43199</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52872</t>
+          <t>52709</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103802</t>
+          <t>104896</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122767</t>
+          <t>122526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>31779</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40660</t>
+          <t>41081</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74057</t>
+          <t>74720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91568</t>
+          <t>91694</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61078</t>
+          <t>61292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72399</t>
+          <t>72603</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>141407</t>
+          <t>140986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>162277</t>
+          <t>161266</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,58%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62779</t>
+          <t>63159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95168</t>
+          <t>96176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42960</t>
+          <t>43629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70265</t>
+          <t>73352</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>112306</t>
+          <t>113738</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>155696</t>
+          <t>154342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>259327</t>
+          <t>258319</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291716</t>
+          <t>291336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>212362</t>
+          <t>209275</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>239667</t>
+          <t>238998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>481427</t>
+          <t>482781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>524817</t>
+          <t>523385</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27356</t>
+          <t>27588</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53518</t>
+          <t>52189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>14127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32749</t>
+          <t>31669</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47831</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79650</t>
+          <t>76482</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>274333</t>
+          <t>275662</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>300495</t>
+          <t>300263</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>207722</t>
+          <t>208802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>226902</t>
+          <t>226344</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>488672</t>
+          <t>491840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>520491</t>
+          <t>521950</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>318451</t>
+          <t>316701</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>384700</t>
+          <t>384864</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>191645</t>
+          <t>189877</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>525085</t>
+          <t>523190</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>613144</t>
+          <t>606579</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1025637</t>
+          <t>1025473</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1091886</t>
+          <t>1093636</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>786267</t>
+          <t>790028</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>840409</t>
+          <t>842177</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1829247</t>
+          <t>1835812</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1917306</t>
+          <t>1919201</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023</t>
+          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37037</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>28459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>52175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157164</t>
+          <t>158127</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178115</t>
+          <t>178724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121587</t>
+          <t>121271</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134113</t>
+          <t>133344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285994</t>
+          <t>286358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>308508</t>
+          <t>310074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32796</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64246</t>
+          <t>62236</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>35272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56613</t>
+          <t>56037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72892</t>
+          <t>74676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110425</t>
+          <t>112568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160051</t>
+          <t>162061</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>191501</t>
+          <t>192792</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100940</t>
+          <t>101516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122207</t>
+          <t>122281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>271424</t>
+          <t>269281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308957</t>
+          <t>307173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62247</t>
+          <t>61526</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37013</t>
+          <t>36789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55372</t>
+          <t>55415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81283</t>
+          <t>82424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111152</t>
+          <t>111932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84549</t>
+          <t>85270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108159</t>
+          <t>107945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65490</t>
+          <t>65447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>84073</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156505</t>
+          <t>155725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186374</t>
+          <t>185233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28415</t>
+          <t>26735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57152</t>
+          <t>55210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31971</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>141046</t>
+          <t>144739</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72314</t>
+          <t>73293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190720</t>
+          <t>193247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111510</t>
+          <t>113452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140247</t>
+          <t>141927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117459</t>
+          <t>113766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>226534</t>
+          <t>224905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236447</t>
+          <t>233920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>354853</t>
+          <t>353874</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15969</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36800</t>
+          <t>36467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89484</t>
+          <t>88503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102344</t>
+          <t>102373</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89738</t>
+          <t>89933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98441</t>
+          <t>98577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183146</t>
+          <t>183479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198402</t>
+          <t>198203</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41019</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50385</t>
+          <t>50931</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73083</t>
+          <t>73696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93279</t>
+          <t>93222</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>111183</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48330</t>
+          <t>48300</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>62845</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>147617</t>
+          <t>147004</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>170315</t>
+          <t>169769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>58325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91254</t>
+          <t>90711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57465</t>
+          <t>58490</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>84393</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122794</t>
+          <t>123445</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163880</t>
+          <t>165044</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>238857</t>
+          <t>239400</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271853</t>
+          <t>271786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217131</t>
+          <t>217216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244144</t>
+          <t>243119</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>467840</t>
+          <t>466676</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>508926</t>
+          <t>508275</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20343</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101637</t>
+          <t>96543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42961</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>70989</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56470</t>
+          <t>49359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162673</t>
+          <t>159228</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>526688</t>
+          <t>531782</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>607982</t>
+          <t>607615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>197810</t>
+          <t>199377</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>227405</t>
+          <t>228021</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>736019</t>
+          <t>739464</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>842222</t>
+          <t>849333</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>221407</t>
+          <t>221500</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>403545</t>
+          <t>403377</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>301871</t>
+          <t>296499</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>435034</t>
+          <t>430214</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>547345</t>
+          <t>547157</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>784691</t>
+          <t>791217</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1537383</t>
+          <t>1537551</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1719521</t>
+          <t>1719428</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1010302</t>
+          <t>1015122</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1143465</t>
+          <t>1148837</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2601573</t>
+          <t>2595047</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2838919</t>
+          <t>2839107</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/P68-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P68-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>31082</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55206</t>
+          <t>55057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39668</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57285</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87415</t>
+          <t>87311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109294</t>
+          <t>109443</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131702</t>
+          <t>133418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71302</t>
+          <t>71422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90310</t>
+          <t>90803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188055</t>
+          <t>188159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218185</t>
+          <t>218912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57228</t>
+          <t>57952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88277</t>
+          <t>87407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42903</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87353</t>
+          <t>88032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124534</t>
+          <t>123846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>182204</t>
+          <t>183074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213253</t>
+          <t>212529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>87713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108477</t>
+          <t>108787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277959</t>
+          <t>278647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315140</t>
+          <t>314461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47044</t>
+          <t>48115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>31355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45207</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73437</t>
+          <t>73430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>127605</t>
+          <t>126534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148700</t>
+          <t>148196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63371</t>
+          <t>62330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79659</t>
+          <t>79060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194898</t>
+          <t>194905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223128</t>
+          <t>221962</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>45567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71928</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32491</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>67917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97637</t>
+          <t>99537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151616</t>
+          <t>150180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177873</t>
+          <t>177977</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102136</t>
+          <t>102506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119095</t>
+          <t>119383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260534</t>
+          <t>258634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292258</t>
+          <t>290254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40856</t>
+          <t>41391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77041</t>
+          <t>77969</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95118</t>
+          <t>95104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>35426</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>45811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118448</t>
+          <t>117913</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138614</t>
+          <t>137864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31335</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54037</t>
+          <t>53629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>22729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44371</t>
+          <t>44451</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70832</t>
+          <t>70875</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,81%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100891</t>
+          <t>101299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123593</t>
+          <t>123584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61787</t>
+          <t>60088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74819</t>
+          <t>73815</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>166914</t>
+          <t>166871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>193375</t>
+          <t>193295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73395</t>
+          <t>72372</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106574</t>
+          <t>105106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,82 +2806,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,3%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>43535</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>32557</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>56792</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>24,24%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>131983</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>112618</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>152514</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>21,85%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>43535</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>31488</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>54986</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>30,62%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>131983</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>113759</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>152953</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>25,61%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229275</t>
+          <t>230743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>262454</t>
+          <t>263477</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,82 +2919,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>136035</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>122778</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>147013</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>75,76%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>81,87%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>383437</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>362906</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>402802</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>74,39%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>70,41%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>78,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>136035</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>124584</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>148082</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>75,76%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>69,38%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>383437</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>362467</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>401661</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>74,39%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90427</t>
+          <t>90611</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126190</t>
+          <t>129267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37611</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64645</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137232</t>
+          <t>135932</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180067</t>
+          <t>181484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>332790</t>
+          <t>329713</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>368553</t>
+          <t>368369</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>174335</t>
+          <t>176966</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>201369</t>
+          <t>200965</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>517893</t>
+          <t>516476</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>560728</t>
+          <t>562028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,52%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>434510</t>
+          <t>430098</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>510003</t>
+          <t>508849</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>196389</t>
+          <t>190991</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>247541</t>
+          <t>247029</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>646055</t>
+          <t>648329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>740870</t>
+          <t>738299</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1383432</t>
+          <t>1384586</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1458925</t>
+          <t>1463337</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>773923</t>
+          <t>774435</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>825075</t>
+          <t>830473</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2174029</t>
+          <t>2176600</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2268844</t>
+          <t>2266570</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29566</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>21911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39674</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57010</t>
+          <t>55608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74754</t>
+          <t>74287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96250</t>
+          <t>95688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47796</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66269</t>
+          <t>65559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127235</t>
+          <t>127404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>156276</t>
+          <t>157678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45092</t>
+          <t>44191</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68872</t>
+          <t>71906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24750</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45858</t>
+          <t>45388</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74619</t>
+          <t>72581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109015</t>
+          <t>107471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103368</t>
+          <t>100334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127148</t>
+          <t>128049</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76830</t>
+          <t>77300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97938</t>
+          <t>98211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185913</t>
+          <t>187457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220309</t>
+          <t>222347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>17438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34600</t>
+          <t>35671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26936</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32619</t>
+          <t>32697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57441</t>
+          <t>56094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108601</t>
+          <t>107530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126435</t>
+          <t>125763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55430</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70968</t>
+          <t>70865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168126</t>
+          <t>169473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192948</t>
+          <t>192870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59230</t>
+          <t>60622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>21021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39215</t>
+          <t>39815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>63002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93020</t>
+          <t>94252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83459</t>
+          <t>82067</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106808</t>
+          <t>106390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63233</t>
+          <t>62633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82448</t>
+          <t>81427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152117</t>
+          <t>150885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182901</t>
+          <t>182135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9793</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>19460</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39933</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58084</t>
+          <t>58330</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72521</t>
+          <t>72842</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50686</t>
+          <t>50776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99092</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119103</t>
+          <t>119565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,0%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33857</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55586</t>
+          <t>56254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47305</t>
+          <t>46846</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72309</t>
+          <t>73619</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61704</t>
+          <t>61036</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83433</t>
+          <t>83686</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32568</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46039</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100273</t>
+          <t>98963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125277</t>
+          <t>125736</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,86%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41211</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69173</t>
+          <t>70470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35259</t>
+          <t>35515</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58738</t>
+          <t>59169</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82341</t>
+          <t>83790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119882</t>
+          <t>119727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>203751</t>
+          <t>202454</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>231713</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>123427</t>
+          <t>122996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146906</t>
+          <t>146650</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>335207</t>
+          <t>335362</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>372748</t>
+          <t>371299</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34971</t>
+          <t>34847</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>60489</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>20840</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>44552</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63251</t>
+          <t>61234</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96853</t>
+          <t>96928</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>301602</t>
+          <t>301743</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>327261</t>
+          <t>327385</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>215944</t>
+          <t>215023</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239230</t>
+          <t>238735</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>524954</t>
+          <t>524879</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>558556</t>
+          <t>560573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>300958</t>
+          <t>298880</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>365159</t>
+          <t>363016</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190759</t>
+          <t>190709</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>242807</t>
+          <t>245637</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>506861</t>
+          <t>505548</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>591211</t>
+          <t>585496</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1053546</t>
+          <t>1055689</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1117747</t>
+          <t>1119825</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>705909</t>
+          <t>703079</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>757957</t>
+          <t>758007</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1776210</t>
+          <t>1781925</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1860560</t>
+          <t>1861873</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47092</t>
+          <t>47335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71889</t>
+          <t>70330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31556</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51027</t>
+          <t>51103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85226</t>
+          <t>84362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115371</t>
+          <t>116877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64277</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89074</t>
+          <t>88831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49948</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69419</t>
+          <t>69891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121770</t>
+          <t>120264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151915</t>
+          <t>152779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69432</t>
+          <t>70079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96238</t>
+          <t>96893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32631</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53593</t>
+          <t>53453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107553</t>
+          <t>109105</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>143725</t>
+          <t>141785</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74059</t>
+          <t>73404</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100865</t>
+          <t>100218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60087</t>
+          <t>60227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81049</t>
+          <t>81792</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140252</t>
+          <t>142192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>176424</t>
+          <t>174872</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30079</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>23820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45893</t>
+          <t>44604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92797</t>
+          <t>91918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108628</t>
+          <t>109189</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62923</t>
+          <t>63860</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76052</t>
+          <t>76182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160319</t>
+          <t>161608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>181421</t>
+          <t>182392</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23450</t>
+          <t>22599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42319</t>
+          <t>42152</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40015</t>
+          <t>39171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49543</t>
+          <t>49116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76432</t>
+          <t>75919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69861</t>
+          <t>70028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88730</t>
+          <t>89581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39962</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>58503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115725</t>
+          <t>116238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142614</t>
+          <t>143041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12866</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56569</t>
+          <t>56792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71548</t>
+          <t>71602</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43199</t>
+          <t>43994</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52709</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104896</t>
+          <t>105200</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122526</t>
+          <t>121944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,07%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41081</t>
+          <t>40404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74720</t>
+          <t>75221</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91694</t>
+          <t>92283</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61292</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72603</t>
+          <t>72095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140986</t>
+          <t>141663</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>161266</t>
+          <t>160936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63159</t>
+          <t>64131</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96176</t>
+          <t>96699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>43539</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73352</t>
+          <t>69833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113738</t>
+          <t>112626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>154342</t>
+          <t>155491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258319</t>
+          <t>257796</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291336</t>
+          <t>290364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>209275</t>
+          <t>212794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>238998</t>
+          <t>239088</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>482781</t>
+          <t>481632</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>523385</t>
+          <t>524497</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52189</t>
+          <t>52895</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31669</t>
+          <t>32225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>45771</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76482</t>
+          <t>76964</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>275662</t>
+          <t>274956</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>300263</t>
+          <t>299216</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>208802</t>
+          <t>208246</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>226344</t>
+          <t>226846</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>491840</t>
+          <t>491358</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>521950</t>
+          <t>522551</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>316701</t>
+          <t>315797</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>384864</t>
+          <t>384409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>189877</t>
+          <t>191223</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242145</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>523190</t>
+          <t>523285</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>606579</t>
+          <t>608126</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1025473</t>
+          <t>1025928</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1093636</t>
+          <t>1094540</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>790028</t>
+          <t>789909</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>842177</t>
+          <t>840831</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1835812</t>
+          <t>1834265</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1919201</t>
+          <t>1919106</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24069</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36074</t>
+          <t>38217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10988</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>39824</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28459</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52175</t>
+          <t>54680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>170132</t>
+          <t>176092</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158127</t>
+          <t>164088</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>178724</t>
+          <t>184029</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>128577</t>
+          <t>136552</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121271</t>
+          <t>130499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133344</t>
+          <t>141281</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>298709</t>
+          <t>312644</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>286358</t>
+          <t>300382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>310074</t>
+          <t>323065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46280</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>34534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>64423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45443</t>
+          <t>46506</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35272</t>
+          <t>37188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56037</t>
+          <t>56787</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>91723</t>
+          <t>94512</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74676</t>
+          <t>75057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112568</t>
+          <t>113607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,44%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>178017</t>
+          <t>185973</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162061</t>
+          <t>169557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192792</t>
+          <t>199446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>112110</t>
+          <t>118959</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>101516</t>
+          <t>108678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>122281</t>
+          <t>128277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>290126</t>
+          <t>304933</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269281</t>
+          <t>285838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>307173</t>
+          <t>324388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>224297</t>
+          <t>233980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>224297</t>
+          <t>233980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224297</t>
+          <t>233980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>157553</t>
+          <t>165465</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>157553</t>
+          <t>165465</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>157553</t>
+          <t>165465</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>399445</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>399445</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>399445</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>49597</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>39859</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61526</t>
+          <t>61359</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45927</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36789</t>
+          <t>37959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55415</t>
+          <t>56111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>95422</t>
+          <t>96560</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82424</t>
+          <t>82515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111932</t>
+          <t>110711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>97301</t>
+          <t>98168</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85270</t>
+          <t>86406</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107945</t>
+          <t>107906</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74935</t>
+          <t>76066</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65447</t>
+          <t>66918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84073</t>
+          <t>85070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>172235</t>
+          <t>174234</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155725</t>
+          <t>160083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185233</t>
+          <t>188279</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>146796</t>
+          <t>147765</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146796</t>
+          <t>147765</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146796</t>
+          <t>147765</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>267657</t>
+          <t>270794</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>267657</t>
+          <t>270794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>267657</t>
+          <t>270794</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>54166</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>73764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>53286</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33600</t>
+          <t>41768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144739</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>121006</t>
+          <t>107451</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73293</t>
+          <t>86564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193247</t>
+          <t>129281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>128309</t>
+          <t>158858</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113452</t>
+          <t>139260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141927</t>
+          <t>175069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>177853</t>
+          <t>127500</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113766</t>
+          <t>114704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224905</t>
+          <t>139018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>306161</t>
+          <t>286359</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233920</t>
+          <t>264529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353874</t>
+          <t>307246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168662</t>
+          <t>213024</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>168662</t>
+          <t>213024</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168662</t>
+          <t>213024</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>258505</t>
+          <t>180786</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>258505</t>
+          <t>180786</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>258505</t>
+          <t>180786</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>427167</t>
+          <t>393810</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>427167</t>
+          <t>393810</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>427167</t>
+          <t>393810</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25736</t>
+          <t>29661</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15774</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28743</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>27119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>45588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96482</t>
+          <t>114504</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88503</t>
+          <t>106497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102373</t>
+          <t>121230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>94721</t>
+          <t>104285</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89933</t>
+          <t>99087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98577</t>
+          <t>108808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>191203</t>
+          <t>218789</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183479</t>
+          <t>208446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198203</t>
+          <t>226915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>105707</t>
+          <t>117876</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105707</t>
+          <t>117876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105707</t>
+          <t>117876</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>219946</t>
+          <t>254034</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>219946</t>
+          <t>254034</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>219946</t>
+          <t>254034</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23115</t>
+          <t>24666</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>42519</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>30582</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38102</t>
+          <t>37908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61831</t>
+          <t>63451</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50931</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73696</t>
+          <t>75245</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>102682</t>
+          <t>102471</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93222</t>
+          <t>92820</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111183</t>
+          <t>110673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>56187</t>
+          <t>56772</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48300</t>
+          <t>49446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62845</t>
+          <t>64423</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>158869</t>
+          <t>159243</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>147004</t>
+          <t>147449</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169769</t>
+          <t>170936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>134298</t>
+          <t>135339</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>134298</t>
+          <t>135339</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>134298</t>
+          <t>135339</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>220700</t>
+          <t>222694</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>220700</t>
+          <t>222694</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>220700</t>
+          <t>222694</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>85851</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58325</t>
+          <t>69236</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>108083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>70527</t>
+          <t>80718</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58490</t>
+          <t>66210</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84393</t>
+          <t>95467</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>143705</t>
+          <t>166568</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123445</t>
+          <t>142794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165044</t>
+          <t>189561</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>256933</t>
+          <t>297310</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239400</t>
+          <t>275078</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>271786</t>
+          <t>313925</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>231082</t>
+          <t>274971</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>217216</t>
+          <t>260222</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>243119</t>
+          <t>289479</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>488015</t>
+          <t>572281</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>466676</t>
+          <t>549288</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>508275</t>
+          <t>596055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>330111</t>
+          <t>383161</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>330111</t>
+          <t>383161</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>330111</t>
+          <t>383161</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>301609</t>
+          <t>355689</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>301609</t>
+          <t>355689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>301609</t>
+          <t>355689</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>631720</t>
+          <t>738849</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>631720</t>
+          <t>738849</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>631720</t>
+          <t>738849</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>56757</t>
+          <t>66654</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20710</t>
+          <t>52042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96543</t>
+          <t>83749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>54710</t>
+          <t>57483</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42345</t>
+          <t>45701</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>70989</t>
+          <t>70173</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>111467</t>
+          <t>124138</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49359</t>
+          <t>105333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>159228</t>
+          <t>145556</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>571568</t>
+          <t>388281</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>531782</t>
+          <t>371186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>607615</t>
+          <t>402893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>215656</t>
+          <t>253913</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>199377</t>
+          <t>241223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>228021</t>
+          <t>265695</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>787225</t>
+          <t>642193</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>739464</t>
+          <t>620775</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>849333</t>
+          <t>660998</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>86,25%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>270366</t>
+          <t>311396</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>270366</t>
+          <t>311396</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>270366</t>
+          <t>311396</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>898692</t>
+          <t>766331</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>898692</t>
+          <t>766331</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>898692</t>
+          <t>766331</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>339505</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>221500</t>
+          <t>345993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>403377</t>
+          <t>427477</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>354215</t>
+          <t>345334</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>296499</t>
+          <t>318644</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>430214</t>
+          <t>374504</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>693720</t>
+          <t>730344</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>547157</t>
+          <t>680340</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>791217</t>
+          <t>782010</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1601423</t>
+          <t>1521659</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1537551</t>
+          <t>1479192</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1719428</t>
+          <t>1560676</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1091121</t>
+          <t>1149017</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1015122</t>
+          <t>1119847</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1148837</t>
+          <t>1175707</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2692544</t>
+          <t>2670676</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2595047</t>
+          <t>2619010</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2839107</t>
+          <t>2720680</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1940928</t>
+          <t>1906669</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1445336</t>
+          <t>1494351</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3386264</t>
+          <t>3401020</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P68-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P68-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2007 (tasa de respuesta: 99,11%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2007 (tasa de respuesta: 99,11%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2012 (tasa de respuesta: 99,41%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2012 (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si piensan que su trabajo les afecta negativamente en 2023 (tasa de respuesta: 98,55%)</t>
+          <t>Población según si piensan que su trabajo afecta negativamente a su salud en 2023 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
